--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488050_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488050_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3332</v>
+        <v>2.4081</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1421</v>
+        <v>5.3293</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.8089</v>
+        <v>-2.9212</v>
       </c>
       <c r="G2" t="n">
         <v>5.1055</v>
@@ -610,13 +610,13 @@
         <v>1.784</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0477</v>
+        <v>-0.9728</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6202</v>
+        <v>-0.433</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4275</v>
+        <v>-0.5399</v>
       </c>
       <c r="V2" t="n">
         <v>-0.337</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7838000000000001</v>
+        <v>1.1279</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4199</v>
+        <v>0.6237</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3638</v>
+        <v>0.5042</v>
       </c>
       <c r="G3" t="n">
         <v>1.2143</v>
@@ -688,13 +688,13 @@
         <v>0.3964</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.49</v>
+        <v>-0.1459</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.312</v>
+        <v>-0.1082</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1781</v>
+        <v>-0.0377</v>
       </c>
       <c r="V3" t="n">
         <v>-0.337</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.628</v>
+        <v>-0.6913</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5071</v>
+        <v>0.3034</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1351</v>
+        <v>-0.9947</v>
       </c>
       <c r="G4" t="n">
         <v>-1.1468</v>
@@ -766,13 +766,13 @@
         <v>0.5947</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2918</v>
+        <v>-0.3552</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2534</v>
+        <v>0.0496</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5452</v>
+        <v>-0.4048</v>
       </c>
       <c r="V4" t="n">
         <v>1.2071</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.3609</v>
+        <v>-0.7235</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2958</v>
+        <v>0.0328</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0651</v>
+        <v>-0.7563</v>
       </c>
       <c r="G5" t="n">
         <v>0.2694</v>
@@ -844,13 +844,13 @@
         <v>0.7929</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.899</v>
+        <v>-0.2616</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5505</v>
+        <v>-0.222</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3484</v>
+        <v>-0.0396</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5331</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3717</v>
+        <v>-1.1493</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3503</v>
+        <v>0.0406</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0214</v>
+        <v>-1.1899</v>
       </c>
       <c r="G6" t="n">
         <v>2.3926</v>
@@ -922,13 +922,13 @@
         <v>0.7929</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1785</v>
+        <v>0.044</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8625</v>
+        <v>-0.4716</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2071</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8556</v>
+        <v>-1.3066</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1895</v>
+        <v>-0.6967</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6661</v>
+        <v>-0.6099</v>
       </c>
       <c r="G7" t="n">
         <v>-0.755</v>
@@ -1000,13 +1000,13 @@
         <v>0.7929</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9023</v>
+        <v>-0.3534</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6864</v>
+        <v>-0.1936</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2159</v>
+        <v>-0.1598</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.5153</v>
+        <v>-2.7065</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9195</v>
+        <v>-1.223</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5958</v>
+        <v>-1.4835</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8487</v>
@@ -1078,13 +1078,13 @@
         <v>1.5858</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.0542</v>
+        <v>-1.2454</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3103</v>
+        <v>-0.6138</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7439</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2071</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.2951</v>
+        <v>-5.1931</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1742</v>
+        <v>-1.1283</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.1209</v>
+        <v>-4.0647</v>
       </c>
       <c r="G9" t="n">
         <v>-3.6176</v>
@@ -1156,13 +1156,13 @@
         <v>1.1893</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9023</v>
+        <v>-0.8003</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5064</v>
+        <v>-0.4606</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3959</v>
+        <v>-0.3397</v>
       </c>
       <c r="V9" t="n">
         <v>1.2071</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4363</v>
+        <v>-5.5352</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.749</v>
+        <v>-5.4829</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3127</v>
+        <v>-0.0523</v>
       </c>
       <c r="G10" t="n">
         <v>-4.3963</v>
@@ -1234,13 +1234,13 @@
         <v>0.7929</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1493</v>
+        <v>0.0504</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6129</v>
+        <v>-0.3468</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7622</v>
+        <v>0.3972</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. GEA BECERRA</t>
+          <t>D. GARZON ALVAREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.2639</v>
+        <v>-6.3253</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5473</v>
+        <v>-5.2643</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7166</v>
+        <v>-1.061</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.9684</v>
+        <v>-4.5554</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.6462</v>
+        <v>-2.028</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3222</v>
+        <v>-2.5273</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9232</v>
+        <v>-3.2413</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.0437</v>
+        <v>-1.3646</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1205</v>
+        <v>-1.8767</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.0452</v>
+        <v>-1.3141</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6024</v>
+        <v>-0.6634</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4428</v>
+        <v>-0.6506</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.9645</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.1538</v>
+        <v>-2.1805</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9287</v>
+        <v>0.0229</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7894</v>
+        <v>-0.1091</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1393</v>
+        <v>0.132</v>
       </c>
       <c r="V11" t="n">
-        <v>1.7403</v>
+        <v>-0.6036</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7403</v>
+        <v>0.2666</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. GARZON ALVAREZ</t>
+          <t>E. GEA BECERRA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4606</v>
+        <v>-7.4157</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.2872</v>
+        <v>-5.4183</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1733</v>
+        <v>-1.9974</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.5554</v>
+        <v>-4.9684</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.028</v>
+        <v>-3.6462</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.5273</v>
+        <v>-1.3222</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.2413</v>
+        <v>-1.9232</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.3646</v>
+        <v>-2.0437</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8767</v>
+        <v>0.1205</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3141</v>
+        <v>-3.0452</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6634</v>
+        <v>-1.6024</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6506</v>
+        <v>-1.4428</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1893</v>
+        <v>-3.9645</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1805</v>
+        <v>-5.1538</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1123</v>
+        <v>-0.223</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.132</v>
+        <v>-0.0815</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0197</v>
+        <v>-0.1415</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6036</v>
+        <v>1.7403</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2666</v>
+        <v>1.7403</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-29.0704</v>
+        <v>-27.5105</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.4437</v>
+        <v>-12.8837</v>
       </c>
       <c r="F13" t="n">
         <v>-14.6267</v>
@@ -1438,13 +1438,13 @@
         <v>-5.3938</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.9127</v>
+        <v>-5.912700000000001</v>
       </c>
       <c r="J13" t="n">
         <v>7.4152</v>
       </c>
       <c r="K13" t="n">
-        <v>1.531300000000001</v>
+        <v>1.5313</v>
       </c>
       <c r="L13" t="n">
         <v>5.884099999999998</v>
@@ -1468,19 +1468,19 @@
         <v>10.9022</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.8001</v>
+        <v>-4.2403</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.5504</v>
+        <v>-2.9906</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2497</v>
+        <v>-1.2498</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.07040000000000013</v>
+        <v>-0.07040000000000024</v>
       </c>
       <c r="W13" t="n">
-        <v>5.487400000000001</v>
+        <v>5.4874</v>
       </c>
       <c r="X13" t="n">
         <v>-5.5577</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.7907</v>
+        <v>10.9629</v>
       </c>
       <c r="E14" t="n">
-        <v>11.2696</v>
+        <v>9.334099999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5211</v>
+        <v>1.6288</v>
       </c>
       <c r="G14" t="n">
         <v>4.4183</v>
@@ -1546,13 +1546,13 @@
         <v>3.7662</v>
       </c>
       <c r="S14" t="n">
-        <v>3.399</v>
+        <v>1.5712</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6727</v>
+        <v>0.7372</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7262999999999999</v>
+        <v>0.834</v>
       </c>
       <c r="V14" t="n">
         <v>1.2071</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.2486</v>
+        <v>9.189</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2187</v>
+        <v>4.1355</v>
       </c>
       <c r="F15" t="n">
-        <v>5.03</v>
+        <v>5.0535</v>
       </c>
       <c r="G15" t="n">
         <v>6.5212</v>
@@ -1624,13 +1624,13 @@
         <v>2.9733</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2548</v>
+        <v>0.6855</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8625</v>
+        <v>0.0543</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6077</v>
+        <v>0.6312</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. CHEKRI KOURAYCHE</t>
+          <t>D. SHERIFF</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.2538</v>
+        <v>6.1555</v>
       </c>
       <c r="E16" t="n">
-        <v>4.6168</v>
+        <v>2.125</v>
       </c>
       <c r="F16" t="n">
-        <v>1.637</v>
+        <v>4.0305</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0652</v>
+        <v>3.6603</v>
       </c>
       <c r="H16" t="n">
-        <v>2.533</v>
+        <v>1.8199</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5322</v>
+        <v>1.8404</v>
       </c>
       <c r="J16" t="n">
-        <v>3.77</v>
+        <v>2.1487</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1797</v>
+        <v>1.2648</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5903</v>
+        <v>0.8839</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7048</v>
+        <v>1.5116</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3533</v>
+        <v>0.5551</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0581</v>
+        <v>0.9565</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5769</v>
+        <v>1.3876</v>
       </c>
       <c r="Q16" t="n">
+        <v>-0.9911</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.3787</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.1076</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.6734</v>
+      </c>
+      <c r="V16" t="n">
         <v>0</v>
       </c>
-      <c r="R16" t="n">
-        <v>2.5769</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.7514</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.5802</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.1712</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-1.1397</v>
-      </c>
       <c r="W16" t="n">
-        <v>0.2666</v>
+        <v>0.5331</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4063</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. SHERIFF</t>
+          <t>F. CHEKRI KOURAYCHE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8825</v>
+        <v>5.6955</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8194</v>
+        <v>4.3112</v>
       </c>
       <c r="F17" t="n">
-        <v>4.0632</v>
+        <v>1.3843</v>
       </c>
       <c r="G17" t="n">
-        <v>3.6603</v>
+        <v>3.0652</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8199</v>
+        <v>2.533</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8404</v>
+        <v>0.5322</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1487</v>
+        <v>3.77</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2648</v>
+        <v>2.1797</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8839</v>
+        <v>1.5903</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5116</v>
+        <v>-0.7048</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5551</v>
+        <v>0.3533</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9565</v>
+        <v>-1.0581</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3876</v>
+        <v>2.5769</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3787</v>
+        <v>2.5769</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8347</v>
+        <v>1.193</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1286</v>
+        <v>0.2746</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.9185</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.1397</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5331</v>
+        <v>0.2666</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5331</v>
+        <v>-1.4063</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. CERISUELO QUESADA</t>
+          <t>M. GAMEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0465</v>
+        <v>0.7403</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2398</v>
+        <v>-1.7649</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1933</v>
+        <v>2.5052</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4572</v>
+        <v>0.4265</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2479</v>
+        <v>-0.9282</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2092</v>
+        <v>1.3546</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5374</v>
+        <v>0.3897</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6133999999999999</v>
+        <v>-0.9478</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9241</v>
+        <v>1.3375</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.9946</v>
+        <v>0.0367</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8613</v>
+        <v>0.0196</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.1333</v>
+        <v>0.0171</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7929</v>
+        <v>0.1982</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R18" t="n">
         <v>2.1805</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6256</v>
+        <v>0.1157</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0721</v>
+        <v>-0.1724</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5534</v>
+        <v>0.288</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6709000000000001</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0864</v>
+        <v>0.1069</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4072</v>
+        <v>-1.1016</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3208</v>
+        <v>1.2085</v>
       </c>
       <c r="G19" t="n">
         <v>1.4151</v>
@@ -1936,13 +1936,13 @@
         <v>1.3876</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3509</v>
+        <v>0.5442</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2275</v>
+        <v>0.0781</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5784</v>
+        <v>0.4661</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2666</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. GAMEZ SANCHEZ</t>
+          <t>J. CERISUELO QUESADA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4912</v>
+        <v>-1.0284</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5798</v>
+        <v>-0.7789</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0886</v>
+        <v>-0.2495</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4265</v>
+        <v>-1.4572</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9282</v>
+        <v>-0.2479</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3546</v>
+        <v>-1.2092</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3897</v>
+        <v>1.5374</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9478</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3375</v>
+        <v>0.9241</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0367</v>
+        <v>-2.9946</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0196</v>
+        <v>-0.8613</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0171</v>
+        <v>-2.1333</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1982</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R20" t="n">
         <v>2.1805</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1159</v>
+        <v>0.5507</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9873</v>
+        <v>0.0534</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1286</v>
+        <v>0.4973</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.0674</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0019</v>
+        <v>-1.6342</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3985</v>
+        <v>-2.1948</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3967</v>
+        <v>0.5606</v>
       </c>
       <c r="G21" t="n">
         <v>-4.5197</v>
@@ -2092,13 +2092,13 @@
         <v>2.7751</v>
       </c>
       <c r="S21" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.4305</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4109</v>
+        <v>-0.2072</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4738</v>
+        <v>0.6377</v>
       </c>
       <c r="V21" t="n">
         <v>0.6709000000000001</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.172</v>
+        <v>-1.7998</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2113</v>
+        <v>-0.0075</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9607</v>
+        <v>-1.7922</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7592</v>
@@ -2170,13 +2170,13 @@
         <v>0.1982</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4713</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.312</v>
+        <v>-0.1082</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1593</v>
+        <v>0.0091</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1397</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>28.47059999999999</v>
+        <v>28.3877</v>
       </c>
       <c r="E23" t="n">
-        <v>14.5675</v>
+        <v>14.0581</v>
       </c>
       <c r="F23" t="n">
-        <v>13.9034</v>
+        <v>14.3297</v>
       </c>
       <c r="G23" t="n">
         <v>12.7705</v>
@@ -2230,7 +2230,7 @@
         <v>11.5557</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.4879</v>
+        <v>-5.487900000000001</v>
       </c>
       <c r="N23" t="n">
         <v>-1.0694</v>
@@ -2248,13 +2248,13 @@
         <v>20.417</v>
       </c>
       <c r="S23" t="n">
-        <v>6.182399999999999</v>
+        <v>6.099299999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>1.6534</v>
+        <v>1.144</v>
       </c>
       <c r="U23" t="n">
-        <v>4.529</v>
+        <v>4.955299999999999</v>
       </c>
       <c r="V23" t="n">
         <v>0.002900000000000347</v>
